--- a/notas_cartao.xlsx
+++ b/notas_cartao.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_134A50D992899BBA14C7EFC9CDB1CF8F35F11C53" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60EB49BD-268B-46D8-8AA0-E72724FFE1C9}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_96E60A376063C3AD2D2A672722BF16F563B882DB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9346B3BF-8966-41EC-8464-B521F00C8BA4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" state="hidden" r:id="rId1"/>
@@ -34,9 +34,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -331,7 +328,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -367,11 +364,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -441,39 +462,41 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -862,13 +885,12 @@
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="28">
-        <f ca="1">TODAY()</f>
-        <v>46152</v>
-      </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
+      <c r="B1" s="33">
+        <v>46149</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -882,61 +904,61 @@
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1">
       <c r="A2" s="3"/>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="29" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="26" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="26"/>
+      <c r="O2" s="36"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25" t="s">
+      <c r="C3" s="36"/>
+      <c r="D3" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="27" t="s">
+      <c r="E3" s="36"/>
+      <c r="F3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27" t="s">
+      <c r="G3" s="36"/>
+      <c r="H3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="27"/>
-      <c r="J3" s="25" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25" t="s">
+      <c r="K3" s="36"/>
+      <c r="L3" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="25"/>
-      <c r="N3" s="26" t="s">
+      <c r="M3" s="36"/>
+      <c r="N3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="26"/>
+      <c r="O3" s="36"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -1801,18 +1823,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="B2:E2"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1845,13 +1867,13 @@
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="33">
-        <f ca="1">Painel!B1</f>
-        <v>46152</v>
-      </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="27">
+        <f>Painel!B1</f>
+        <v>46149</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -1865,61 +1887,61 @@
     </row>
     <row r="2" spans="1:15" ht="21.75" customHeight="1">
       <c r="A2" s="3"/>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="35" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="34" t="s">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="26" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="26"/>
+      <c r="O2" s="36"/>
     </row>
     <row r="3" spans="1:15" ht="18.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31" t="s">
+      <c r="C3" s="37"/>
+      <c r="D3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="32" t="s">
+      <c r="E3" s="37"/>
+      <c r="F3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32" t="s">
+      <c r="G3" s="37"/>
+      <c r="H3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="31" t="s">
+      <c r="I3" s="37"/>
+      <c r="J3" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31" t="s">
+      <c r="K3" s="37"/>
+      <c r="L3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="31"/>
-      <c r="N3" s="26" t="s">
+      <c r="M3" s="37"/>
+      <c r="N3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="26"/>
+      <c r="O3" s="36"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -2716,18 +2738,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="B2:E2"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
